--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,83 +5131,83 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.45</v>
+        <v>3.16</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="R37" t="n">
-        <v>2.87</v>
+        <v>2.11</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.56</v>
+        <v>3.55</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.26</v>
+        <v>3.34</v>
       </c>
       <c r="R42" t="n">
-        <v>2.42</v>
+        <v>1.93</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.56</v>
+        <v>3.55</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.26</v>
+        <v>3.34</v>
       </c>
       <c r="R41" t="n">
-        <v>2.42</v>
+        <v>1.93</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI97"/>
+  <dimension ref="A1:BI95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4885,27 +4885,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>46164.54166666666</v>
+        <v>46164.5</v>
       </c>
     </row>
     <row r="24">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>46164.58333333334</v>
+        <v>46164.54166666666</v>
       </c>
     </row>
     <row r="25">
@@ -5476,27 +5476,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3" t="n">
-        <v>46164.625</v>
+        <v>46164.58333333334</v>
       </c>
     </row>
     <row r="27">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7643,27 +7643,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7831,7 +7831,7 @@
         <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
-        <v>46164.65625</v>
+        <v>46164.625</v>
       </c>
     </row>
     <row r="38">
@@ -7840,27 +7840,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8028,7 +8028,7 @@
         <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
-        <v>46164.65625</v>
+        <v>46164.625</v>
       </c>
     </row>
     <row r="39">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.45</v>
+        <v>3.55</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="R40" t="n">
-        <v>2.87</v>
+        <v>1.93</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.55</v>
+        <v>2.56</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.34</v>
+        <v>3.26</v>
       </c>
       <c r="R41" t="n">
-        <v>1.93</v>
+        <v>2.42</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9219,12 +9219,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="BI45" s="3" t="n">
-        <v>46164.66666666666</v>
+        <v>46164.65625</v>
       </c>
     </row>
     <row r="46">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9604,7 +9604,7 @@
         <v>0</v>
       </c>
       <c r="BI46" s="3" t="n">
-        <v>46164.66666666666</v>
+        <v>46164.65625</v>
       </c>
     </row>
     <row r="47">
@@ -9810,12 +9810,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9998,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="BI48" s="3" t="n">
-        <v>46164.67708333334</v>
+        <v>46164.66666666666</v>
       </c>
     </row>
     <row r="49">
@@ -10007,12 +10007,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10195,7 +10195,7 @@
         <v>0</v>
       </c>
       <c r="BI49" s="3" t="n">
-        <v>46164.67708333334</v>
+        <v>46164.66666666666</v>
       </c>
     </row>
     <row r="50">
@@ -10401,12 +10401,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10589,7 +10589,7 @@
         <v>0</v>
       </c>
       <c r="BI51" s="3" t="n">
-        <v>46164.79166666666</v>
+        <v>46164.67708333334</v>
       </c>
     </row>
     <row r="52">
@@ -10598,12 +10598,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10786,7 +10786,7 @@
         <v>0</v>
       </c>
       <c r="BI52" s="3" t="n">
-        <v>46164.83333333334</v>
+        <v>46164.67708333334</v>
       </c>
     </row>
     <row r="53">
@@ -10795,27 +10795,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10983,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="BI53" s="3" t="n">
-        <v>46164.875</v>
+        <v>46164.79166666666</v>
       </c>
     </row>
     <row r="54">
@@ -10992,12 +10992,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11180,7 +11180,7 @@
         <v>0</v>
       </c>
       <c r="BI54" s="3" t="n">
-        <v>46164.875</v>
+        <v>46164.83333333334</v>
       </c>
     </row>
     <row r="55">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18872,27 +18872,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19060,7 +19060,7 @@
         <v>0</v>
       </c>
       <c r="BI94" s="3" t="n">
-        <v>46164.875</v>
+        <v>46164.89583333334</v>
       </c>
     </row>
     <row r="95">
@@ -19069,27 +19069,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19257,400 +19257,6 @@
         <v>0</v>
       </c>
       <c r="BI95" s="3" t="n">
-        <v>46164.875</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="n">
-        <v>46164</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Tulsa Roughnecks</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Hartford Athletic</t>
-        </is>
-      </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N96" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P96" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R96" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="S96" t="n">
-        <v>0</v>
-      </c>
-      <c r="T96" t="n">
-        <v>0</v>
-      </c>
-      <c r="U96" t="n">
-        <v>0</v>
-      </c>
-      <c r="V96" t="n">
-        <v>0</v>
-      </c>
-      <c r="W96" t="n">
-        <v>0</v>
-      </c>
-      <c r="X96" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y96" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE96" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF96" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ96" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA96" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB96" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC96" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD96" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE96" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF96" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG96" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH96" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI96" s="3" t="n">
-        <v>46164.89583333334</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="n">
-        <v>46164</v>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Tacoma Defiance</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>LA Galaxy II</t>
-        </is>
-      </c>
-      <c r="G97" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N97" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P97" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
-      <c r="R97" t="n">
-        <v>0</v>
-      </c>
-      <c r="S97" t="n">
-        <v>0</v>
-      </c>
-      <c r="T97" t="n">
-        <v>0</v>
-      </c>
-      <c r="U97" t="n">
-        <v>0</v>
-      </c>
-      <c r="V97" t="n">
-        <v>0</v>
-      </c>
-      <c r="W97" t="n">
-        <v>0</v>
-      </c>
-      <c r="X97" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y97" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ97" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA97" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB97" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC97" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD97" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE97" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF97" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG97" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH97" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI97" s="3" t="n">
         <v>46164.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI95"/>
+  <dimension ref="A1:BI94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.16</v>
+        <v>2.56</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="R44" t="n">
-        <v>2.11</v>
+        <v>2.42</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18675,27 +18675,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18863,7 +18863,7 @@
         <v>0</v>
       </c>
       <c r="BI93" s="3" t="n">
-        <v>46164.875</v>
+        <v>46164.89583333334</v>
       </c>
     </row>
     <row r="94">
@@ -18872,12 +18872,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF94" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19060,203 +19060,6 @@
         <v>0</v>
       </c>
       <c r="BI94" s="3" t="n">
-        <v>46164.89583333334</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="n">
-        <v>46164</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Tacoma Defiance</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>LA Galaxy II</t>
-        </is>
-      </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" t="n">
-        <v>0</v>
-      </c>
-      <c r="M95" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N95" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P95" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
-      <c r="R95" t="n">
-        <v>0</v>
-      </c>
-      <c r="S95" t="n">
-        <v>0</v>
-      </c>
-      <c r="T95" t="n">
-        <v>0</v>
-      </c>
-      <c r="U95" t="n">
-        <v>0</v>
-      </c>
-      <c r="V95" t="n">
-        <v>0</v>
-      </c>
-      <c r="W95" t="n">
-        <v>0</v>
-      </c>
-      <c r="X95" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y95" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ95" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA95" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB95" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC95" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD95" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE95" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF95" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG95" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH95" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI95" s="3" t="n">
         <v>46164.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3.16</v>
+        <v>2.56</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="R39" t="n">
-        <v>2.11</v>
+        <v>2.42</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G92" t="n">

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.55</v>
+        <v>3.16</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.34</v>
+        <v>3.24</v>
       </c>
       <c r="R42" t="n">
-        <v>1.93</v>
+        <v>2.11</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.16</v>
+        <v>3.55</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.24</v>
+        <v>3.34</v>
       </c>
       <c r="R46" t="n">
-        <v>2.11</v>
+        <v>1.93</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14390,7 +14390,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G92" t="n">

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.37</v>
+        <v>3.75</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7</v>
+        <v>4.05</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.76</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.75</v>
+        <v>3.37</v>
       </c>
       <c r="R17" t="n">
-        <v>4.05</v>
+        <v>2.7</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.45</v>
+        <v>3.16</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="R44" t="n">
-        <v>2.87</v>
+        <v>2.11</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="R46" t="n">
-        <v>1.93</v>
+        <v>2.87</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14390,7 +14390,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G92" t="n">

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.76</v>
+        <v>2.45</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.75</v>
+        <v>3.37</v>
       </c>
       <c r="R16" t="n">
-        <v>4.05</v>
+        <v>2.7</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.91</v>
+        <v>2.39</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>3.98</v>
+        <v>2.93</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.39</v>
+        <v>1.91</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R22" t="n">
-        <v>2.93</v>
+        <v>3.98</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.45</v>
+        <v>3.55</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="R46" t="n">
-        <v>2.87</v>
+        <v>1.93</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G92" t="n">

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.37</v>
+        <v>3.75</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7</v>
+        <v>4.05</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.91</v>
+        <v>3.13</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R22" t="n">
-        <v>3.98</v>
+        <v>2.16</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.56</v>
+        <v>3.58</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.26</v>
+        <v>3.45</v>
       </c>
       <c r="R41" t="n">
-        <v>2.42</v>
+        <v>2.01</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.45</v>
+        <v>3.55</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="R42" t="n">
-        <v>2.87</v>
+        <v>1.93</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3.16</v>
+        <v>2.93</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="R43" t="n">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>8.35</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G91" t="n">

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI94"/>
+  <dimension ref="A1:BI90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.76</v>
+        <v>2.45</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.75</v>
+        <v>3.37</v>
       </c>
       <c r="R16" t="n">
-        <v>4.05</v>
+        <v>2.7</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.91</v>
+        <v>3.13</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R21" t="n">
-        <v>3.98</v>
+        <v>2.16</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.13</v>
+        <v>1.91</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R22" t="n">
-        <v>2.16</v>
+        <v>3.98</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.56</v>
+        <v>2.93</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="R39" t="n">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.55</v>
+        <v>2.56</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.34</v>
+        <v>3.26</v>
       </c>
       <c r="R42" t="n">
-        <v>1.93</v>
+        <v>2.42</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.93</v>
+        <v>2.45</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="R43" t="n">
-        <v>2.24</v>
+        <v>2.87</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.45</v>
+        <v>3.55</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="R45" t="n">
-        <v>2.87</v>
+        <v>1.93</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17887,27 +17887,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18075,7 +18075,7 @@
         <v>0</v>
       </c>
       <c r="BI89" s="3" t="n">
-        <v>46164.875</v>
+        <v>46164.89583333334</v>
       </c>
     </row>
     <row r="90">
@@ -18084,27 +18084,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18272,794 +18272,6 @@
         <v>0</v>
       </c>
       <c r="BI90" s="3" t="n">
-        <v>46164.875</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="n">
-        <v>46164</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Croatia Prva HNL</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Rijeka</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Gorica</t>
-        </is>
-      </c>
-      <c r="G91" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N91" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
-      <c r="R91" t="n">
-        <v>0</v>
-      </c>
-      <c r="S91" t="n">
-        <v>0</v>
-      </c>
-      <c r="T91" t="n">
-        <v>0</v>
-      </c>
-      <c r="U91" t="n">
-        <v>0</v>
-      </c>
-      <c r="V91" t="n">
-        <v>0</v>
-      </c>
-      <c r="W91" t="n">
-        <v>0</v>
-      </c>
-      <c r="X91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ91" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA91" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB91" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC91" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD91" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE91" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF91" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG91" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH91" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI91" s="3" t="n">
-        <v>46164.875</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="n">
-        <v>46164</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Rangers</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Santiago Wanderers</t>
-        </is>
-      </c>
-      <c r="G92" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N92" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
-      <c r="R92" t="n">
-        <v>0</v>
-      </c>
-      <c r="S92" t="n">
-        <v>0</v>
-      </c>
-      <c r="T92" t="n">
-        <v>0</v>
-      </c>
-      <c r="U92" t="n">
-        <v>0</v>
-      </c>
-      <c r="V92" t="n">
-        <v>0</v>
-      </c>
-      <c r="W92" t="n">
-        <v>0</v>
-      </c>
-      <c r="X92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ92" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA92" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB92" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC92" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD92" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE92" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF92" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG92" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH92" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI92" s="3" t="n">
-        <v>46164.875</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="n">
-        <v>46164</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Tulsa Roughnecks</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Hartford Athletic</t>
-        </is>
-      </c>
-      <c r="G93" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N93" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P93" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R93" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="S93" t="n">
-        <v>0</v>
-      </c>
-      <c r="T93" t="n">
-        <v>0</v>
-      </c>
-      <c r="U93" t="n">
-        <v>0</v>
-      </c>
-      <c r="V93" t="n">
-        <v>0</v>
-      </c>
-      <c r="W93" t="n">
-        <v>0</v>
-      </c>
-      <c r="X93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE93" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF93" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ93" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA93" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB93" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC93" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD93" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE93" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF93" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG93" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH93" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI93" s="3" t="n">
-        <v>46164.89583333334</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="n">
-        <v>46164</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Tacoma Defiance</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>LA Galaxy II</t>
-        </is>
-      </c>
-      <c r="G94" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N94" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P94" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
-      <c r="R94" t="n">
-        <v>0</v>
-      </c>
-      <c r="S94" t="n">
-        <v>0</v>
-      </c>
-      <c r="T94" t="n">
-        <v>0</v>
-      </c>
-      <c r="U94" t="n">
-        <v>0</v>
-      </c>
-      <c r="V94" t="n">
-        <v>0</v>
-      </c>
-      <c r="W94" t="n">
-        <v>0</v>
-      </c>
-      <c r="X94" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y94" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ94" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA94" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB94" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC94" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD94" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE94" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF94" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG94" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH94" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI94" s="3" t="n">
         <v>46164.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.91</v>
+        <v>3.13</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R22" t="n">
-        <v>3.98</v>
+        <v>2.16</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.93</v>
+        <v>2.56</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="R39" t="n">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.58</v>
+        <v>4.72</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="R41" t="n">
-        <v>2.01</v>
+        <v>1.63</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.56</v>
+        <v>2.93</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="R42" t="n">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.45</v>
+        <v>3.16</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="R43" t="n">
-        <v>2.87</v>
+        <v>2.11</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="R45" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.16</v>
+        <v>2.45</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="R46" t="n">
-        <v>2.11</v>
+        <v>2.87</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G88" t="n">

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI90"/>
+  <dimension ref="A1:BI86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.37</v>
+        <v>3.75</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7</v>
+        <v>4.05</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.39</v>
+        <v>3.13</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="R18" t="n">
-        <v>2.93</v>
+        <v>2.16</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R19" t="n">
-        <v>3.98</v>
+        <v>3.73</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.13</v>
+        <v>2.39</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="R22" t="n">
-        <v>2.16</v>
+        <v>2.93</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R23" t="n">
-        <v>3.73</v>
+        <v>3.98</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5673,27 +5673,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5861,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="BI27" s="3" t="n">
-        <v>46164.625</v>
+        <v>46164.58333333334</v>
       </c>
     </row>
     <row r="28">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8037,27 +8037,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.56</v>
+        <v>1.95</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="R39" t="n">
-        <v>2.42</v>
+        <v>3.97</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="BI39" s="3" t="n">
-        <v>46164.65625</v>
+        <v>46164.625</v>
       </c>
     </row>
     <row r="40">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>4.72</v>
+        <v>2.56</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.65</v>
+        <v>3.26</v>
       </c>
       <c r="R41" t="n">
-        <v>1.63</v>
+        <v>2.42</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.55</v>
+        <v>4.72</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.34</v>
+        <v>3.65</v>
       </c>
       <c r="R44" t="n">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.99</v>
+        <v>1.79</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.58</v>
+        <v>2.45</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.45</v>
+        <v>3.22</v>
       </c>
       <c r="R45" t="n">
-        <v>2.01</v>
+        <v>2.87</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.45</v>
+        <v>2.93</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="R46" t="n">
-        <v>2.87</v>
+        <v>2.24</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9613,12 +9613,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.34</v>
+        <v>3.55</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.95</v>
+        <v>3.34</v>
       </c>
       <c r="R47" t="n">
-        <v>8.35</v>
+        <v>1.93</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9801,7 +9801,7 @@
         <v>0</v>
       </c>
       <c r="BI47" s="3" t="n">
-        <v>46164.66666666666</v>
+        <v>46164.65625</v>
       </c>
     </row>
     <row r="48">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>8.35</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10204,12 +10204,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10392,7 +10392,7 @@
         <v>0</v>
       </c>
       <c r="BI50" s="3" t="n">
-        <v>46164.67708333334</v>
+        <v>46164.66666666666</v>
       </c>
     </row>
     <row r="51">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="BI53" s="3" t="n">
-        <v>46164.79166666666</v>
+        <v>46164.67708333334</v>
       </c>
     </row>
     <row r="54">
@@ -10992,12 +10992,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11180,7 +11180,7 @@
         <v>0</v>
       </c>
       <c r="BI54" s="3" t="n">
-        <v>46164.83333333334</v>
+        <v>46164.79166666666</v>
       </c>
     </row>
     <row r="55">
@@ -11189,27 +11189,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11377,7 +11377,7 @@
         <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
-        <v>46164.875</v>
+        <v>46164.83333333334</v>
       </c>
     </row>
     <row r="56">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17099,27 +17099,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17287,7 +17287,7 @@
         <v>0</v>
       </c>
       <c r="BI85" s="3" t="n">
-        <v>46164.875</v>
+        <v>46164.89583333334</v>
       </c>
     </row>
     <row r="86">
@@ -17296,27 +17296,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17484,794 +17484,6 @@
         <v>0</v>
       </c>
       <c r="BI86" s="3" t="n">
-        <v>46164.875</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="n">
-        <v>46164</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Croatia Prva HNL</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Dinamo Zagreb</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Lokomotiva Zagreb</t>
-        </is>
-      </c>
-      <c r="G87" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N87" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
-      <c r="R87" t="n">
-        <v>0</v>
-      </c>
-      <c r="S87" t="n">
-        <v>0</v>
-      </c>
-      <c r="T87" t="n">
-        <v>0</v>
-      </c>
-      <c r="U87" t="n">
-        <v>0</v>
-      </c>
-      <c r="V87" t="n">
-        <v>0</v>
-      </c>
-      <c r="W87" t="n">
-        <v>0</v>
-      </c>
-      <c r="X87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI87" s="3" t="n">
-        <v>46164.875</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="n">
-        <v>46164</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Coquimbo Unido</t>
-        </is>
-      </c>
-      <c r="G88" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N88" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
-      <c r="R88" t="n">
-        <v>0</v>
-      </c>
-      <c r="S88" t="n">
-        <v>0</v>
-      </c>
-      <c r="T88" t="n">
-        <v>0</v>
-      </c>
-      <c r="U88" t="n">
-        <v>0</v>
-      </c>
-      <c r="V88" t="n">
-        <v>0</v>
-      </c>
-      <c r="W88" t="n">
-        <v>0</v>
-      </c>
-      <c r="X88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI88" s="3" t="n">
-        <v>46164.875</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="n">
-        <v>46164</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Tulsa Roughnecks</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Hartford Athletic</t>
-        </is>
-      </c>
-      <c r="G89" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N89" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P89" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R89" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="S89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T89" t="n">
-        <v>0</v>
-      </c>
-      <c r="U89" t="n">
-        <v>0</v>
-      </c>
-      <c r="V89" t="n">
-        <v>0</v>
-      </c>
-      <c r="W89" t="n">
-        <v>0</v>
-      </c>
-      <c r="X89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE89" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF89" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ89" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA89" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB89" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC89" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD89" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE89" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF89" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG89" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH89" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI89" s="3" t="n">
-        <v>46164.89583333334</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="n">
-        <v>46164</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Tacoma Defiance</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>LA Galaxy II</t>
-        </is>
-      </c>
-      <c r="G90" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N90" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" t="n">
-        <v>0</v>
-      </c>
-      <c r="T90" t="n">
-        <v>0</v>
-      </c>
-      <c r="U90" t="n">
-        <v>0</v>
-      </c>
-      <c r="V90" t="n">
-        <v>0</v>
-      </c>
-      <c r="W90" t="n">
-        <v>0</v>
-      </c>
-      <c r="X90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ90" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA90" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB90" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC90" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD90" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE90" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF90" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG90" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH90" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI90" s="3" t="n">
         <v>46164.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.37</v>
+        <v>3.75</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7</v>
+        <v>4.05</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.76</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.75</v>
+        <v>3.37</v>
       </c>
       <c r="R17" t="n">
-        <v>4.05</v>
+        <v>2.7</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.13</v>
+        <v>2.39</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="R18" t="n">
-        <v>2.16</v>
+        <v>2.93</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3.58</v>
+        <v>3.16</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.45</v>
+        <v>3.24</v>
       </c>
       <c r="R40" t="n">
-        <v>2.01</v>
+        <v>2.11</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.56</v>
+        <v>3.58</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.26</v>
+        <v>3.45</v>
       </c>
       <c r="R41" t="n">
-        <v>2.42</v>
+        <v>2.01</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3.16</v>
+        <v>4.72</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.24</v>
+        <v>3.65</v>
       </c>
       <c r="R43" t="n">
-        <v>2.11</v>
+        <v>1.63</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>4.72</v>
+        <v>2.93</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="R44" t="n">
-        <v>1.63</v>
+        <v>2.24</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.79</v>
+        <v>1.99</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.93</v>
+        <v>2.56</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="R46" t="n">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="R47" t="n">
-        <v>1.93</v>
+        <v>2.87</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>8.35</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>8.35</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.13</v>
+        <v>1.91</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R20" t="n">
-        <v>2.16</v>
+        <v>3.98</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.94</v>
+        <v>3.13</v>
       </c>
       <c r="Q21" t="n">
         <v>3.35</v>
       </c>
       <c r="R21" t="n">
-        <v>3.73</v>
+        <v>2.16</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R23" t="n">
-        <v>3.98</v>
+        <v>3.73</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3.16</v>
+        <v>2.45</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="R40" t="n">
-        <v>2.11</v>
+        <v>2.87</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.58</v>
+        <v>4.72</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="R41" t="n">
-        <v>2.01</v>
+        <v>1.63</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>4.72</v>
+        <v>2.93</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="R43" t="n">
-        <v>1.63</v>
+        <v>2.24</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.79</v>
+        <v>1.99</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.93</v>
+        <v>3.58</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="R44" t="n">
-        <v>2.24</v>
+        <v>2.01</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.56</v>
+        <v>3.16</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="R46" t="n">
-        <v>2.42</v>
+        <v>2.11</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G84" t="n">

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.39</v>
+        <v>1.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>2.93</v>
+        <v>3.98</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R20" t="n">
-        <v>3.98</v>
+        <v>3.73</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.13</v>
+        <v>2.39</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>2.16</v>
+        <v>2.93</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.95</v>
+        <v>4.06</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.4</v>
+        <v>3.77</v>
       </c>
       <c r="R28" t="n">
-        <v>3.97</v>
+        <v>1.75</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6171,10 +6171,10 @@
         <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>4.72</v>
+        <v>2.45</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.65</v>
+        <v>3.22</v>
       </c>
       <c r="R41" t="n">
-        <v>1.63</v>
+        <v>2.87</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.58</v>
+        <v>3.16</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.45</v>
+        <v>3.24</v>
       </c>
       <c r="R44" t="n">
-        <v>2.01</v>
+        <v>2.11</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.56</v>
+        <v>3.58</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.26</v>
+        <v>3.45</v>
       </c>
       <c r="R45" t="n">
-        <v>2.42</v>
+        <v>2.01</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.16</v>
+        <v>2.56</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="R46" t="n">
-        <v>2.11</v>
+        <v>2.42</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>8.35</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>8.35</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G84" t="n">

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.76</v>
+        <v>2.45</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.75</v>
+        <v>3.37</v>
       </c>
       <c r="R16" t="n">
-        <v>4.05</v>
+        <v>2.7</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.13</v>
+        <v>2.39</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>2.16</v>
+        <v>2.93</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.94</v>
+        <v>3.13</v>
       </c>
       <c r="Q20" t="n">
         <v>3.35</v>
       </c>
       <c r="R20" t="n">
-        <v>3.73</v>
+        <v>2.16</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.39</v>
+        <v>1.94</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="R21" t="n">
-        <v>2.93</v>
+        <v>3.73</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6171,10 +6171,10 @@
         <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6368,10 +6368,10 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.45</v>
+        <v>3.58</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.22</v>
+        <v>3.45</v>
       </c>
       <c r="R41" t="n">
-        <v>2.87</v>
+        <v>2.01</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.55</v>
+        <v>2.56</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.34</v>
+        <v>3.26</v>
       </c>
       <c r="R42" t="n">
-        <v>1.93</v>
+        <v>2.42</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.16</v>
+        <v>2.45</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="R44" t="n">
-        <v>2.11</v>
+        <v>2.87</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.56</v>
+        <v>3.16</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="R46" t="n">
-        <v>2.42</v>
+        <v>2.11</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>4.72</v>
+        <v>3.55</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.65</v>
+        <v>3.34</v>
       </c>
       <c r="R47" t="n">
-        <v>1.63</v>
+        <v>1.93</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.79</v>
+        <v>1.99</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G84" t="n">

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.37</v>
+        <v>3.75</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7</v>
+        <v>4.05</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.91</v>
+        <v>3.13</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R18" t="n">
-        <v>3.98</v>
+        <v>2.16</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.13</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="R20" t="n">
-        <v>2.16</v>
+        <v>3.24</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R21" t="n">
-        <v>3.73</v>
+        <v>3.98</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6368,10 +6368,10 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.95</v>
+        <v>5.64</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="R35" t="n">
-        <v>3.97</v>
+        <v>1.43</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,16 +7347,16 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>4.06</v>
+        <v>1.95</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.77</v>
+        <v>3.4</v>
       </c>
       <c r="R37" t="n">
-        <v>1.75</v>
+        <v>3.97</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8141,10 +8141,10 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>4.72</v>
+        <v>2.56</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.65</v>
+        <v>3.26</v>
       </c>
       <c r="R40" t="n">
-        <v>1.63</v>
+        <v>2.42</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.58</v>
+        <v>3.16</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.45</v>
+        <v>3.24</v>
       </c>
       <c r="R41" t="n">
-        <v>2.01</v>
+        <v>2.11</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.56</v>
+        <v>4.72</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.26</v>
+        <v>3.65</v>
       </c>
       <c r="R42" t="n">
-        <v>2.42</v>
+        <v>1.63</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.93</v>
+        <v>3.58</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="R43" t="n">
-        <v>2.24</v>
+        <v>2.01</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.45</v>
+        <v>3.55</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="R44" t="n">
-        <v>2.87</v>
+        <v>1.93</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.16</v>
+        <v>2.93</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="R46" t="n">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="R47" t="n">
-        <v>1.93</v>
+        <v>2.87</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G84" t="n">

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.37</v>
+        <v>3.75</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7</v>
+        <v>4.05</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.13</v>
+        <v>2.39</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="R18" t="n">
-        <v>2.16</v>
+        <v>2.93</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.39</v>
+        <v>1.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="R19" t="n">
-        <v>2.93</v>
+        <v>3.73</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.91</v>
+        <v>3.13</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R21" t="n">
-        <v>3.98</v>
+        <v>2.16</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>5.64</v>
+        <v>4.06</v>
       </c>
       <c r="Q35" t="n">
-        <v>5</v>
+        <v>3.77</v>
       </c>
       <c r="R35" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7353,10 +7353,10 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7550,10 +7550,10 @@
         <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="R37" t="n">
-        <v>3.97</v>
+        <v>2.67</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8141,10 +8141,10 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.16</v>
+        <v>2.93</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="R41" t="n">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>4.72</v>
+        <v>3.55</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.65</v>
+        <v>3.34</v>
       </c>
       <c r="R42" t="n">
-        <v>1.63</v>
+        <v>1.93</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.79</v>
+        <v>1.99</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3.58</v>
+        <v>4.72</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="R43" t="n">
-        <v>2.01</v>
+        <v>1.63</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="R44" t="n">
-        <v>1.93</v>
+        <v>2.87</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.34</v>
+        <v>3.16</v>
       </c>
       <c r="Q45" t="n">
-        <v>5.2</v>
+        <v>3.24</v>
       </c>
       <c r="R45" t="n">
-        <v>7.75</v>
+        <v>2.11</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.93</v>
+        <v>1.34</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="R46" t="n">
-        <v>2.24</v>
+        <v>7.75</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.45</v>
+        <v>3.58</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.22</v>
+        <v>3.45</v>
       </c>
       <c r="R47" t="n">
-        <v>2.87</v>
+        <v>2.01</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.34</v>
+        <v>2.77</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.95</v>
+        <v>3.54</v>
       </c>
       <c r="R48" t="n">
-        <v>8.35</v>
+        <v>2.36</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.77</v>
+        <v>1.34</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.54</v>
+        <v>4.95</v>
       </c>
       <c r="R50" t="n">
-        <v>2.36</v>
+        <v>8.35</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G84" t="n">

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.37</v>
+        <v>3.75</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7</v>
+        <v>4.05</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.76</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.75</v>
+        <v>3.37</v>
       </c>
       <c r="R17" t="n">
-        <v>4.05</v>
+        <v>2.7</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="R19" t="n">
-        <v>3.73</v>
+        <v>3.24</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>3.13</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="R20" t="n">
-        <v>3.24</v>
+        <v>2.16</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R23" t="n">
-        <v>3.98</v>
+        <v>3.73</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5974,10 +5974,10 @@
         <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6565,10 +6565,10 @@
         <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7550,10 +7550,10 @@
         <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.56</v>
+        <v>3.16</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="R40" t="n">
-        <v>2.42</v>
+        <v>2.11</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.93</v>
+        <v>1.34</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="R41" t="n">
-        <v>2.24</v>
+        <v>7.75</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.55</v>
+        <v>2.56</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.34</v>
+        <v>3.26</v>
       </c>
       <c r="R42" t="n">
-        <v>1.93</v>
+        <v>2.42</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>4.72</v>
+        <v>2.45</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.65</v>
+        <v>3.22</v>
       </c>
       <c r="R43" t="n">
-        <v>1.63</v>
+        <v>2.87</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.45</v>
+        <v>2.93</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="R44" t="n">
-        <v>2.87</v>
+        <v>2.24</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.16</v>
+        <v>3.58</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.24</v>
+        <v>3.45</v>
       </c>
       <c r="R45" t="n">
-        <v>2.11</v>
+        <v>2.01</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.34</v>
+        <v>4.72</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.2</v>
+        <v>3.65</v>
       </c>
       <c r="R46" t="n">
-        <v>7.75</v>
+        <v>1.63</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="R47" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.23</v>
+        <v>2.63</v>
       </c>
       <c r="Q51" t="n">
-        <v>6.55</v>
+        <v>4</v>
       </c>
       <c r="R51" t="n">
-        <v>9.199999999999999</v>
+        <v>2.05</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="Q52" t="n">
         <v>4</v>
       </c>
       <c r="R52" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10702,10 +10702,10 @@
         <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.5</v>
+        <v>1.23</v>
       </c>
       <c r="Q53" t="n">
-        <v>4</v>
+        <v>6.55</v>
       </c>
       <c r="R53" t="n">
-        <v>2.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G84" t="n">

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.37</v>
+        <v>3.75</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7</v>
+        <v>4.05</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.39</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="R18" t="n">
-        <v>2.93</v>
+        <v>3.73</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.91</v>
+        <v>2.39</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R22" t="n">
-        <v>3.98</v>
+        <v>2.93</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="R23" t="n">
-        <v>3.73</v>
+        <v>3.24</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.68</v>
+        <v>2.26</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="R28" t="n">
-        <v>4.08</v>
+        <v>2.67</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5974,10 +5974,10 @@
         <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6565,10 +6565,10 @@
         <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7156,10 +7156,10 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>4.06</v>
+        <v>1.95</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.77</v>
+        <v>3.4</v>
       </c>
       <c r="R38" t="n">
-        <v>1.75</v>
+        <v>3.97</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8141,10 +8141,10 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="R42" t="n">
-        <v>2.42</v>
+        <v>2.87</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.45</v>
+        <v>4.72</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.22</v>
+        <v>3.65</v>
       </c>
       <c r="R43" t="n">
-        <v>2.87</v>
+        <v>1.63</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.93</v>
+        <v>3.55</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="R44" t="n">
-        <v>2.24</v>
+        <v>1.93</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.58</v>
+        <v>2.93</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="R45" t="n">
-        <v>2.01</v>
+        <v>2.24</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>4.72</v>
+        <v>3.58</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="R46" t="n">
-        <v>1.63</v>
+        <v>2.01</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF46" t="n">
         <v>1.79</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>1.96</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3.55</v>
+        <v>2.56</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.34</v>
+        <v>3.26</v>
       </c>
       <c r="R47" t="n">
-        <v>1.93</v>
+        <v>2.42</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.77</v>
+        <v>1.34</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.54</v>
+        <v>4.95</v>
       </c>
       <c r="R49" t="n">
-        <v>2.36</v>
+        <v>8.35</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>8.35</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.63</v>
+        <v>1.23</v>
       </c>
       <c r="Q51" t="n">
-        <v>4</v>
+        <v>6.55</v>
       </c>
       <c r="R51" t="n">
-        <v>2.05</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="Q52" t="n">
         <v>4</v>
       </c>
       <c r="R52" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10702,10 +10702,10 @@
         <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.23</v>
+        <v>2.5</v>
       </c>
       <c r="Q53" t="n">
-        <v>6.55</v>
+        <v>4</v>
       </c>
       <c r="R53" t="n">
-        <v>9.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G84" t="n">

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.37</v>
+        <v>3.75</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7</v>
+        <v>4.05</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.76</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.75</v>
+        <v>3.37</v>
       </c>
       <c r="R17" t="n">
-        <v>4.05</v>
+        <v>2.7</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>2.39</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="R18" t="n">
-        <v>3.73</v>
+        <v>2.93</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.13</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="R20" t="n">
-        <v>2.16</v>
+        <v>3.24</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.91</v>
+        <v>3.13</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R21" t="n">
-        <v>3.98</v>
+        <v>2.16</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.39</v>
+        <v>1.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="R22" t="n">
-        <v>2.93</v>
+        <v>3.73</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.26</v>
+        <v>1.68</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="R28" t="n">
-        <v>2.67</v>
+        <v>4.08</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5974,10 +5974,10 @@
         <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7156,10 +7156,10 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.95</v>
+        <v>5.64</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="R38" t="n">
-        <v>3.97</v>
+        <v>1.43</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,16 +7938,16 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>5.64</v>
+        <v>2.26</v>
       </c>
       <c r="Q39" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="R39" t="n">
-        <v>1.43</v>
+        <v>2.67</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8141,10 +8141,10 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3.16</v>
+        <v>2.93</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="R40" t="n">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.34</v>
+        <v>4.72</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.2</v>
+        <v>3.65</v>
       </c>
       <c r="R41" t="n">
-        <v>7.75</v>
+        <v>1.63</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.45</v>
+        <v>3.58</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.22</v>
+        <v>3.45</v>
       </c>
       <c r="R42" t="n">
-        <v>2.87</v>
+        <v>2.01</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>4.72</v>
+        <v>2.45</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.65</v>
+        <v>3.22</v>
       </c>
       <c r="R43" t="n">
-        <v>1.63</v>
+        <v>2.87</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.55</v>
+        <v>3.16</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.34</v>
+        <v>3.24</v>
       </c>
       <c r="R44" t="n">
-        <v>1.93</v>
+        <v>2.11</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.93</v>
+        <v>3.55</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="R45" t="n">
-        <v>2.24</v>
+        <v>1.93</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.58</v>
+        <v>1.34</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.45</v>
+        <v>5.2</v>
       </c>
       <c r="R46" t="n">
-        <v>2.01</v>
+        <v>7.75</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.23</v>
+        <v>2.63</v>
       </c>
       <c r="Q51" t="n">
-        <v>6.55</v>
+        <v>4</v>
       </c>
       <c r="R51" t="n">
-        <v>9.199999999999999</v>
+        <v>2.05</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="Q52" t="n">
         <v>4</v>
       </c>
       <c r="R52" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10702,10 +10702,10 @@
         <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.5</v>
+        <v>1.23</v>
       </c>
       <c r="Q53" t="n">
-        <v>4</v>
+        <v>6.55</v>
       </c>
       <c r="R53" t="n">
-        <v>2.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G84" t="n">

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.39</v>
+        <v>1.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>2.93</v>
+        <v>3.98</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R19" t="n">
-        <v>3.98</v>
+        <v>3.73</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.94</v>
+        <v>2.39</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="R22" t="n">
-        <v>3.73</v>
+        <v>2.93</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="R30" t="n">
-        <v>3.97</v>
+        <v>2.67</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>5.64</v>
+        <v>1.95</v>
       </c>
       <c r="Q38" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="R38" t="n">
-        <v>1.43</v>
+        <v>3.97</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,16 +7938,16 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.26</v>
+        <v>5.64</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="R39" t="n">
-        <v>2.67</v>
+        <v>1.43</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8141,10 +8141,10 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.93</v>
+        <v>3.58</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="R40" t="n">
-        <v>2.24</v>
+        <v>2.01</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>4.72</v>
+        <v>2.56</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.65</v>
+        <v>3.26</v>
       </c>
       <c r="R41" t="n">
-        <v>1.63</v>
+        <v>2.42</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.58</v>
+        <v>1.34</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.45</v>
+        <v>5.2</v>
       </c>
       <c r="R42" t="n">
-        <v>2.01</v>
+        <v>7.75</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.16</v>
+        <v>2.93</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="R44" t="n">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.34</v>
+        <v>3.16</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.2</v>
+        <v>3.24</v>
       </c>
       <c r="R46" t="n">
-        <v>7.75</v>
+        <v>2.11</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.56</v>
+        <v>4.72</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.26</v>
+        <v>3.65</v>
       </c>
       <c r="R47" t="n">
-        <v>2.42</v>
+        <v>1.63</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.77</v>
+        <v>1.34</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.54</v>
+        <v>4.95</v>
       </c>
       <c r="R48" t="n">
-        <v>2.36</v>
+        <v>8.35</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.34</v>
+        <v>2.77</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.95</v>
+        <v>3.54</v>
       </c>
       <c r="R49" t="n">
-        <v>8.35</v>
+        <v>2.36</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.63</v>
+        <v>1.23</v>
       </c>
       <c r="Q51" t="n">
-        <v>4</v>
+        <v>6.55</v>
       </c>
       <c r="R51" t="n">
-        <v>2.05</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.23</v>
+        <v>2.63</v>
       </c>
       <c r="Q53" t="n">
-        <v>6.55</v>
+        <v>4</v>
       </c>
       <c r="R53" t="n">
-        <v>9.199999999999999</v>
+        <v>2.05</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12223,7 +12223,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G84" t="n">

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="R3" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,70 +1401,70 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.75</v>
+        <v>3.93</v>
       </c>
       <c r="R16" t="n">
-        <v>4.05</v>
+        <v>4.47</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.45</v>
+        <v>2.97</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.37</v>
+        <v>3.28</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7</v>
+        <v>2.31</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3962,121 +3962,121 @@
         <v>3.98</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB18" t="n">
         <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD18" t="n">
         <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,22 +4150,22 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="R19" t="n">
-        <v>3.73</v>
+        <v>3.24</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4174,10 +4174,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -4189,40 +4189,40 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4267,13 +4267,13 @@
         <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD19" t="n">
         <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,61 +4347,61 @@
         </is>
       </c>
       <c r="P20" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T20" t="n">
         <v>2</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="U20" t="n">
         <v>3.55</v>
       </c>
-      <c r="R20" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -4410,67 +4410,67 @@
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BB20" t="n">
         <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BD20" t="n">
         <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,130 +4544,130 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BB21" t="n">
         <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD21" t="n">
         <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,130 +4938,130 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.13</v>
+        <v>1.94</v>
       </c>
       <c r="Q23" t="n">
         <v>3.35</v>
       </c>
       <c r="R23" t="n">
-        <v>2.16</v>
+        <v>3.72</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB23" t="n">
         <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD23" t="n">
         <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF23" t="n">
         <v>0</v>
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5974,10 +5974,10 @@
         <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7353,10 +7353,10 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>4.06</v>
+        <v>1.95</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.77</v>
+        <v>3.4</v>
       </c>
       <c r="R36" t="n">
-        <v>1.75</v>
+        <v>3.97</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8141,10 +8141,10 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="R40" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.56</v>
+        <v>1.34</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.26</v>
+        <v>5.2</v>
       </c>
       <c r="R41" t="n">
-        <v>2.42</v>
+        <v>7.75</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.34</v>
+        <v>3.58</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.2</v>
+        <v>3.45</v>
       </c>
       <c r="R42" t="n">
-        <v>7.75</v>
+        <v>2.01</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.55</v>
+        <v>3.16</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.34</v>
+        <v>3.24</v>
       </c>
       <c r="R45" t="n">
-        <v>1.93</v>
+        <v>2.11</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.16</v>
+        <v>2.56</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="R46" t="n">
-        <v>2.11</v>
+        <v>2.42</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.23</v>
+        <v>2.5</v>
       </c>
       <c r="Q51" t="n">
-        <v>6.55</v>
+        <v>4</v>
       </c>
       <c r="R51" t="n">
-        <v>9.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10505,10 +10505,10 @@
         <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.5</v>
+        <v>1.23</v>
       </c>
       <c r="Q52" t="n">
-        <v>4</v>
+        <v>6.55</v>
       </c>
       <c r="R52" t="n">
-        <v>2.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10702,10 +10702,10 @@
         <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12223,7 +12223,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G84" t="n">

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1204,70 +1204,70 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,70 +1401,70 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.76</v>
+        <v>3.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.29</v>
+        <v>2.98</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.8</v>
+        <v>1.93</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="R9" t="n">
-        <v>2.55</v>
+        <v>3.8</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2852,52 +2852,52 @@
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU12" t="n">
         <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3174,124 +3174,124 @@
         <v>2.7</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,22 +3362,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.64</v>
+        <v>3.93</v>
       </c>
       <c r="R15" t="n">
-        <v>3.74</v>
+        <v>4.47</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="T15" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="U15" t="n">
-        <v>4.34</v>
+        <v>4.81</v>
       </c>
       <c r="V15" t="n">
         <v>1.3</v>
@@ -3386,55 +3386,55 @@
         <v>3.16</v>
       </c>
       <c r="X15" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AA15" t="n">
         <v>1.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.05</v>
+        <v>3.96</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AF15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL15" t="n">
         <v>2.11</v>
       </c>
-      <c r="AG15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.19</v>
-      </c>
       <c r="AM15" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,16 +3476,16 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="BD15" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="BF15" t="n">
         <v>1.22</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,22 +3559,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.93</v>
+        <v>3.64</v>
       </c>
       <c r="R16" t="n">
-        <v>4.47</v>
+        <v>3.74</v>
       </c>
       <c r="S16" t="n">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.27</v>
+        <v>2.36</v>
       </c>
       <c r="U16" t="n">
-        <v>4.81</v>
+        <v>4.34</v>
       </c>
       <c r="V16" t="n">
         <v>1.3</v>
@@ -3583,55 +3583,55 @@
         <v>3.16</v>
       </c>
       <c r="X16" t="n">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA16" t="n">
         <v>1.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.96</v>
+        <v>4.05</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.45</v>
+        <v>4.9</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,16 +3673,16 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="BF16" t="n">
         <v>1.22</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,130 +3953,130 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="R18" t="n">
-        <v>3.98</v>
+        <v>3.24</v>
       </c>
       <c r="S18" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="U18" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="V18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.8</v>
+        <v>2.18</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.15</v>
+        <v>4.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.97</v>
+        <v>1.55</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.45</v>
+        <v>2.38</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="AI18" t="n">
-        <v>6.25</v>
+        <v>4.1</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.78</v>
+        <v>1.46</v>
       </c>
       <c r="AL18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
         <v>1.86</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.58</v>
       </c>
       <c r="BF18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,130 +4150,130 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="R19" t="n">
-        <v>3.24</v>
+        <v>3.72</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="T19" t="n">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="U19" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X19" t="n">
-        <v>2.18</v>
+        <v>2.65</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AD19" t="n">
-        <v>4.25</v>
+        <v>3.35</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.38</v>
+        <v>3.15</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AI19" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.38</v>
+        <v>1.98</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB19" t="n">
         <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="BD19" t="n">
         <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="BF19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,130 +4347,130 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.39</v>
+        <v>3.13</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="R20" t="n">
-        <v>2.93</v>
+        <v>2.16</v>
       </c>
       <c r="S20" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="T20" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW20" t="n">
         <v>2</v>
       </c>
-      <c r="U20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ20" t="n">
+      <c r="AX20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.5</v>
       </c>
       <c r="BF20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,130 +4544,130 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.13</v>
+        <v>2.39</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>2.16</v>
+        <v>2.93</v>
       </c>
       <c r="S21" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="T21" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="V21" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="W21" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="X21" t="n">
-        <v>2.63</v>
+        <v>3.05</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
         <v>1.38</v>
       </c>
-      <c r="Z21" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AD21" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.84</v>
+        <v>2.17</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="AH21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM21" t="n">
         <v>1.3</v>
       </c>
-      <c r="AI21" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK21" t="n">
+      <c r="AN21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AW21" t="n">
         <v>1.64</v>
       </c>
-      <c r="AL21" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW21" t="n">
+      <c r="AX21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ21" t="n">
         <v>2</v>
       </c>
-      <c r="AX21" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ21" t="n">
+      <c r="BA21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
         <v>2.38</v>
       </c>
-      <c r="BA21" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.05</v>
-      </c>
       <c r="BD21" t="n">
         <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="BF21" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,130 +4938,130 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R23" t="n">
-        <v>3.72</v>
+        <v>3.98</v>
       </c>
       <c r="S23" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="T23" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U23" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="V23" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W23" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="X23" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z23" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI23" t="n">
         <v>6.25</v>
       </c>
-      <c r="AA23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AJ23" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="AM23" t="n">
         <v>1.27</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.55</v>
+        <v>2.32</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.55</v>
+        <v>3.6</v>
       </c>
       <c r="BB23" t="n">
         <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="BD23" t="n">
         <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="BF23" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6171,10 +6171,10 @@
         <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.95</v>
+        <v>4.06</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.4</v>
+        <v>3.77</v>
       </c>
       <c r="R36" t="n">
-        <v>3.97</v>
+        <v>1.75</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3.55</v>
+        <v>2.56</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.34</v>
+        <v>3.26</v>
       </c>
       <c r="R40" t="n">
-        <v>1.93</v>
+        <v>2.42</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.34</v>
+        <v>2.93</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="R41" t="n">
-        <v>7.75</v>
+        <v>2.24</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.58</v>
+        <v>3.16</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.45</v>
+        <v>3.24</v>
       </c>
       <c r="R42" t="n">
-        <v>2.01</v>
+        <v>2.11</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.45</v>
+        <v>1.34</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.22</v>
+        <v>5.2</v>
       </c>
       <c r="R43" t="n">
-        <v>2.87</v>
+        <v>7.75</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.93</v>
+        <v>3.55</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="R44" t="n">
-        <v>2.24</v>
+        <v>1.93</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.16</v>
+        <v>3.58</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.24</v>
+        <v>3.45</v>
       </c>
       <c r="R45" t="n">
-        <v>2.11</v>
+        <v>2.01</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.56</v>
+        <v>4.72</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.26</v>
+        <v>3.65</v>
       </c>
       <c r="R46" t="n">
-        <v>2.42</v>
+        <v>1.63</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>4.72</v>
+        <v>2.45</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.65</v>
+        <v>3.22</v>
       </c>
       <c r="R47" t="n">
-        <v>1.63</v>
+        <v>2.87</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G84" t="n">

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI86"/>
+  <dimension ref="A1:BI87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="R2" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="S2" t="n">
         <v>2.82</v>
@@ -825,7 +825,7 @@
         <v>3.12</v>
       </c>
       <c r="X2" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="Y2" t="n">
         <v>1.49</v>
@@ -840,22 +840,22 @@
         <v>1.03</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.42</v>
+        <v>4.2</v>
       </c>
       <c r="AE2" t="n">
         <v>1.61</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AI2" t="n">
         <v>4.4</v>
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1204,70 +1204,70 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.38</v>
+        <v>1.89</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="U4" t="n">
-        <v>4.55</v>
+        <v>5.22</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="W4" t="n">
-        <v>2.82</v>
+        <v>3.68</v>
       </c>
       <c r="X4" t="n">
-        <v>2.7</v>
+        <v>2.11</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.85</v>
+        <v>4.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.5</v>
+        <v>5.45</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.86</v>
+        <v>1.54</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.9</v>
+        <v>2.56</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.04</v>
+        <v>2.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.29</v>
+        <v>1.64</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.9</v>
+        <v>3.44</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.07</v>
+        <v>1.23</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.04</v>
+        <v>1.63</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.94</v>
+        <v>5.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.69</v>
+        <v>2.11</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,70 +1401,70 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV7" t="n">
         <v>2.1</v>
       </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="R9" t="n">
-        <v>3.8</v>
+        <v>4.95</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.76</v>
+        <v>1.93</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.29</v>
+        <v>2.95</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="S10" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>4.33</v>
+        <v>2.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.4</v>
+        <v>3.29</v>
       </c>
       <c r="R12" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="S12" t="n">
-        <v>5.33</v>
+        <v>3.38</v>
       </c>
       <c r="T12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.99</v>
       </c>
-      <c r="U12" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AF12" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AI12" t="n">
-        <v>7.1</v>
+        <v>6.55</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.77</v>
+        <v>1.96</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2852,52 +2852,52 @@
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
         <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE12" t="n">
         <v>1.61</v>
       </c>
-      <c r="AY12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.57</v>
-      </c>
       <c r="BF12" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.87</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="R13" t="n">
-        <v>4.95</v>
+        <v>2.7</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="S14" t="n">
-        <v>3.74</v>
+        <v>5.33</v>
       </c>
       <c r="T14" t="n">
-        <v>1.66</v>
+        <v>1.99</v>
       </c>
       <c r="U14" t="n">
-        <v>4.05</v>
+        <v>2.41</v>
       </c>
       <c r="V14" t="n">
-        <v>1.76</v>
+        <v>1.43</v>
       </c>
       <c r="W14" t="n">
-        <v>1.94</v>
+        <v>2.53</v>
       </c>
       <c r="X14" t="n">
-        <v>4.3</v>
+        <v>3.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="Z14" t="n">
-        <v>15</v>
+        <v>7.8</v>
       </c>
       <c r="AA14" t="n">
         <v>1.02</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="AC14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR14" t="n">
         <v>1.72</v>
       </c>
-      <c r="AD14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AS14" t="n">
-        <v>2.95</v>
+        <v>2.14</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.55</v>
+        <v>1.98</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.08</v>
+        <v>2.24</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.44</v>
+        <v>3.34</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,22 +3362,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.93</v>
+        <v>3.64</v>
       </c>
       <c r="R15" t="n">
-        <v>4.47</v>
+        <v>3.74</v>
       </c>
       <c r="S15" t="n">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.27</v>
+        <v>2.36</v>
       </c>
       <c r="U15" t="n">
-        <v>4.81</v>
+        <v>4.34</v>
       </c>
       <c r="V15" t="n">
         <v>1.3</v>
@@ -3386,55 +3386,55 @@
         <v>3.16</v>
       </c>
       <c r="X15" t="n">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA15" t="n">
         <v>1.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.96</v>
+        <v>4.05</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AI15" t="n">
-        <v>4.45</v>
+        <v>4.9</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,16 +3476,16 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="BF15" t="n">
         <v>1.22</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,22 +3559,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.64</v>
+        <v>3.93</v>
       </c>
       <c r="R16" t="n">
-        <v>3.74</v>
+        <v>4.47</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="T16" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="U16" t="n">
-        <v>4.34</v>
+        <v>4.81</v>
       </c>
       <c r="V16" t="n">
         <v>1.3</v>
@@ -3583,55 +3583,55 @@
         <v>3.16</v>
       </c>
       <c r="X16" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AA16" t="n">
         <v>1.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.05</v>
+        <v>3.96</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AF16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL16" t="n">
         <v>2.11</v>
       </c>
-      <c r="AG16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.19</v>
-      </c>
       <c r="AM16" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,16 +3673,16 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="BD16" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="BF16" t="n">
         <v>1.22</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="R18" t="n">
-        <v>3.24</v>
+        <v>3.72</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="T18" t="n">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="U18" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X18" t="n">
-        <v>2.18</v>
+        <v>2.65</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AD18" t="n">
-        <v>4.25</v>
+        <v>3.35</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.38</v>
+        <v>3.15</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.38</v>
+        <v>1.98</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.94</v>
+        <v>3.13</v>
       </c>
       <c r="Q19" t="n">
         <v>3.35</v>
       </c>
       <c r="R19" t="n">
-        <v>3.72</v>
+        <v>2.16</v>
       </c>
       <c r="S19" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="T19" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U19" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="V19" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W19" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="X19" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="Y19" t="n">
         <v>1.38</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.25</v>
+        <v>6.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="AH19" t="n">
         <v>1.3</v>
       </c>
       <c r="AI19" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AK19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR19" t="n">
         <v>1.68</v>
       </c>
-      <c r="AL19" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AS19" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.65</v>
+        <v>2.38</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.55</v>
+        <v>1.73</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.13</v>
+        <v>1.91</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R20" t="n">
-        <v>2.16</v>
+        <v>3.98</v>
       </c>
       <c r="S20" t="n">
-        <v>3.25</v>
+        <v>2.43</v>
       </c>
       <c r="T20" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="U20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X20" t="n">
         <v>2.8</v>
       </c>
-      <c r="V20" t="n">
+      <c r="Y20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY20" t="n">
         <v>1.32</v>
       </c>
-      <c r="W20" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
+      <c r="AZ20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BB20" t="n">
         <v>1.26</v>
       </c>
-      <c r="AD20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>0</v>
-      </c>
       <c r="BC20" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4580,7 +4580,7 @@
         <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC21" t="n">
         <v>1.38</v>
@@ -4601,10 +4601,10 @@
         <v>1.21</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK21" t="n">
         <v>1.85</v>
@@ -4658,19 +4658,19 @@
         <v>2.06</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC21" t="n">
         <v>2.38</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE21" t="n">
         <v>1.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,22 +4741,22 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4765,10 +4765,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -4780,40 +4780,40 @@
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4858,13 +4858,13 @@
         <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD22" t="n">
         <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,130 +4938,130 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
         <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
         <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5962,40 +5962,40 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.93</v>
+        <v>1.29</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.77</v>
+        <v>3.1</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,55 +6120,55 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.68</v>
+        <v>5.64</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="R29" t="n">
-        <v>4.08</v>
+        <v>1.43</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AG29" t="n">
         <v>1.86</v>
@@ -6177,22 +6177,22 @@
         <v>1.89</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6234,19 +6234,19 @@
         <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,79 +6514,79 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.26</v>
+        <v>1.74</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="R31" t="n">
-        <v>2.67</v>
+        <v>3.27</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6628,19 +6628,19 @@
         <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,79 +6908,79 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7022,19 +7022,19 @@
         <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,79 +7302,79 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>5.64</v>
+        <v>4.06</v>
       </c>
       <c r="Q35" t="n">
-        <v>5</v>
+        <v>3.77</v>
       </c>
       <c r="R35" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.86</v>
+        <v>2.48</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7416,19 +7416,19 @@
         <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.56</v>
+        <v>4.72</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.26</v>
+        <v>3.65</v>
       </c>
       <c r="R40" t="n">
-        <v>2.42</v>
+        <v>1.63</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.93</v>
+        <v>3.16</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="R41" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.16</v>
+        <v>2.56</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="R42" t="n">
-        <v>2.11</v>
+        <v>2.42</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W43" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X43" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY43" t="n">
         <v>1.34</v>
       </c>
-      <c r="Q43" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="R43" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.55</v>
+        <v>2.93</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="R44" t="n">
-        <v>1.93</v>
+        <v>2.24</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="R45" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,79 +9469,79 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>4.72</v>
+        <v>1.33</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.65</v>
+        <v>5.25</v>
       </c>
       <c r="R46" t="n">
-        <v>1.63</v>
+        <v>8</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>6.92</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.79</v>
+        <v>1.46</v>
       </c>
       <c r="AF46" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AL46" t="n">
         <v>1.96</v>
       </c>
-      <c r="AG46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>0</v>
-      </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9550,52 +9550,52 @@
         <v>0</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS46" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AU46" t="n">
         <v>0</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW46" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY46" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BA46" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BF46" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,133 +9666,133 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="Q47" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R47" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W47" t="n">
         <v>3.22</v>
       </c>
-      <c r="R47" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0</v>
-      </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR47" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AS47" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AX47" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BA47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BB47" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC47" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF47" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.34</v>
+        <v>3.5</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.95</v>
+        <v>3.52</v>
       </c>
       <c r="R48" t="n">
-        <v>8.35</v>
+        <v>1.98</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -9998,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="BI48" s="3" t="n">
-        <v>46164.66666666666</v>
+        <v>46164.65625</v>
       </c>
     </row>
     <row r="49">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,79 +10060,79 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
@@ -10141,52 +10141,52 @@
         <v>0</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR49" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS49" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AU49" t="n">
         <v>0</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AY49" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BA49" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="BB49" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC49" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD49" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE49" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BF49" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10257,7 +10257,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="Q50" t="n">
         <v>3.54</v>
@@ -10266,70 +10266,70 @@
         <v>2.36</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN50" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
@@ -10338,52 +10338,52 @@
         <v>0</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR50" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS50" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU50" t="n">
         <v>0</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW50" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BA50" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BB50" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC50" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BD50" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="BE50" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BF50" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10505,10 +10505,10 @@
         <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -10589,7 +10589,7 @@
         <v>0</v>
       </c>
       <c r="BI51" s="3" t="n">
-        <v>46164.67708333334</v>
+        <v>46164.66666666666</v>
       </c>
     </row>
     <row r="52">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.23</v>
+        <v>2.63</v>
       </c>
       <c r="Q52" t="n">
-        <v>6.55</v>
+        <v>4</v>
       </c>
       <c r="R52" t="n">
-        <v>9.199999999999999</v>
+        <v>2.05</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.63</v>
+        <v>1.23</v>
       </c>
       <c r="Q53" t="n">
-        <v>4</v>
+        <v>6.55</v>
       </c>
       <c r="R53" t="n">
-        <v>2.05</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10992,12 +10992,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,61 +11045,61 @@
         </is>
       </c>
       <c r="P54" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>4</v>
+      </c>
+      <c r="R54" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q54" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="R54" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>0</v>
-      </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -11180,7 +11180,7 @@
         <v>0</v>
       </c>
       <c r="BI54" s="3" t="n">
-        <v>46164.79166666666</v>
+        <v>46164.67708333334</v>
       </c>
     </row>
     <row r="55">
@@ -11189,12 +11189,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11377,7 +11377,7 @@
         <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
-        <v>46164.83333333334</v>
+        <v>46164.79166666666</v>
       </c>
     </row>
     <row r="56">
@@ -11386,27 +11386,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -11574,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="BI56" s="3" t="n">
-        <v>46164.875</v>
+        <v>46164.83333333334</v>
       </c>
     </row>
     <row r="57">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14390,7 +14390,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P71" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17099,12 +17099,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17287,7 +17287,7 @@
         <v>0</v>
       </c>
       <c r="BI85" s="3" t="n">
-        <v>46164.89583333334</v>
+        <v>46164.875</v>
       </c>
     </row>
     <row r="86">
@@ -17296,12 +17296,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17484,6 +17484,203 @@
         <v>0</v>
       </c>
       <c r="BI86" s="3" t="n">
+        <v>46164.89583333334</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Tacoma Defiance</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>LA Galaxy II</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N87" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" t="n">
+        <v>0</v>
+      </c>
+      <c r="U87" t="n">
+        <v>0</v>
+      </c>
+      <c r="V87" t="n">
+        <v>0</v>
+      </c>
+      <c r="W87" t="n">
+        <v>0</v>
+      </c>
+      <c r="X87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI87" s="3" t="n">
         <v>46164.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.98</v>
+        <v>3.4</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2064,52 +2064,52 @@
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU8" t="n">
         <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.87</v>
+        <v>2.76</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.94</v>
+        <v>3.29</v>
       </c>
       <c r="R9" t="n">
-        <v>4.95</v>
+        <v>2.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.93</v>
+        <v>3</v>
       </c>
       <c r="Q10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="X10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AS10" t="n">
         <v>2.95</v>
       </c>
-      <c r="R10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AY10" t="n">
         <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.76</v>
+        <v>1.93</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.29</v>
+        <v>2.95</v>
       </c>
       <c r="R12" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="S12" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.7</v>
+        <v>2.98</v>
       </c>
       <c r="R13" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3246,52 +3246,52 @@
         <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
         <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,22 +3362,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.64</v>
+        <v>3.93</v>
       </c>
       <c r="R15" t="n">
-        <v>3.74</v>
+        <v>4.47</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="T15" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="U15" t="n">
-        <v>4.34</v>
+        <v>4.81</v>
       </c>
       <c r="V15" t="n">
         <v>1.3</v>
@@ -3386,55 +3386,55 @@
         <v>3.16</v>
       </c>
       <c r="X15" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AA15" t="n">
         <v>1.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.05</v>
+        <v>3.96</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AF15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL15" t="n">
         <v>2.11</v>
       </c>
-      <c r="AG15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.19</v>
-      </c>
       <c r="AM15" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,16 +3476,16 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="BD15" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="BF15" t="n">
         <v>1.22</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.67</v>
+        <v>2.97</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.93</v>
+        <v>3.28</v>
       </c>
       <c r="R16" t="n">
-        <v>4.47</v>
+        <v>2.31</v>
       </c>
       <c r="S16" t="n">
-        <v>2.21</v>
+        <v>3.5</v>
       </c>
       <c r="T16" t="n">
-        <v>2.27</v>
+        <v>2.07</v>
       </c>
       <c r="U16" t="n">
-        <v>4.81</v>
+        <v>2.72</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W16" t="n">
-        <v>3.16</v>
+        <v>2.85</v>
       </c>
       <c r="X16" t="n">
-        <v>2.39</v>
+        <v>2.69</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.6</v>
+        <v>6.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.96</v>
+        <v>3.42</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.52</v>
+        <v>3.05</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.45</v>
+        <v>5.95</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.97</v>
+        <v>1.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.28</v>
+        <v>3.64</v>
       </c>
       <c r="R17" t="n">
-        <v>2.31</v>
+        <v>3.74</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.07</v>
+        <v>2.36</v>
       </c>
       <c r="U17" t="n">
-        <v>2.72</v>
+        <v>4.34</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W17" t="n">
-        <v>2.85</v>
+        <v>3.16</v>
       </c>
       <c r="X17" t="n">
-        <v>2.69</v>
+        <v>2.44</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.42</v>
+        <v>4.05</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AI17" t="n">
-        <v>5.95</v>
+        <v>4.9</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="BD17" t="n">
         <v>4</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.13</v>
+        <v>1.91</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R19" t="n">
-        <v>2.16</v>
+        <v>3.98</v>
       </c>
       <c r="S19" t="n">
-        <v>3.25</v>
+        <v>2.43</v>
       </c>
       <c r="T19" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="U19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X19" t="n">
         <v>2.8</v>
       </c>
-      <c r="V19" t="n">
+      <c r="Y19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY19" t="n">
         <v>1.32</v>
       </c>
-      <c r="W19" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC19" t="n">
+      <c r="AZ19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BB19" t="n">
         <v>1.26</v>
       </c>
-      <c r="AD19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.19</v>
-      </c>
       <c r="BC19" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="R20" t="n">
-        <v>3.98</v>
+        <v>3.24</v>
       </c>
       <c r="S20" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="T20" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="U20" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="V20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.8</v>
+        <v>2.18</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.15</v>
+        <v>4.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.97</v>
+        <v>1.55</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.45</v>
+        <v>2.38</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="AI20" t="n">
-        <v>6.25</v>
+        <v>4.1</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.78</v>
+        <v>1.46</v>
       </c>
       <c r="AL20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
         <v>1.86</v>
       </c>
-      <c r="AM20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.58</v>
-      </c>
       <c r="BF20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW22" t="n">
         <v>2</v>
       </c>
-      <c r="Q22" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R22" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T22" t="n">
+      <c r="AX22" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ22" t="n">
         <v>2.38</v>
       </c>
-      <c r="U22" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>0</v>
-      </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5962,40 +5962,40 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.74</v>
+        <v>4.06</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.92</v>
+        <v>3.77</v>
       </c>
       <c r="R31" t="n">
-        <v>3.27</v>
+        <v>1.75</v>
       </c>
       <c r="S31" t="n">
-        <v>2.17</v>
+        <v>4.14</v>
       </c>
       <c r="T31" t="n">
-        <v>2.58</v>
+        <v>2.29</v>
       </c>
       <c r="U31" t="n">
-        <v>3.96</v>
+        <v>2.36</v>
       </c>
       <c r="V31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W31" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC31" t="n">
         <v>1.17</v>
       </c>
-      <c r="W31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AA31" t="n">
+      <c r="AD31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN31" t="n">
         <v>1.21</v>
       </c>
-      <c r="AB31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD31" t="n">
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BD31" t="n">
         <v>4.7</v>
       </c>
-      <c r="AE31" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BE31" t="n">
-        <v>2.27</v>
+        <v>1.88</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,79 +6711,79 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6825,19 +6825,19 @@
         <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,79 +6908,79 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7022,19 +7022,19 @@
         <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,79 +7302,79 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7416,19 +7416,19 @@
         <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7538,40 +7538,40 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,79 +7696,79 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
@@ -7810,19 +7810,19 @@
         <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>4.72</v>
+        <v>3.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.65</v>
+        <v>3.52</v>
       </c>
       <c r="R40" t="n">
-        <v>1.63</v>
+        <v>1.98</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.56</v>
+        <v>1.33</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.26</v>
+        <v>5.25</v>
       </c>
       <c r="R42" t="n">
-        <v>2.42</v>
+        <v>8</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>6.92</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.91</v>
+        <v>1.46</v>
       </c>
       <c r="AF42" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AX42" t="n">
         <v>1.85</v>
       </c>
-      <c r="AG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>0</v>
-      </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.78</v>
+        <v>2.93</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="R43" t="n">
-        <v>2.48</v>
+        <v>2.24</v>
       </c>
       <c r="S43" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AG43" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN43" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AS43" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AT43" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AU43" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV43" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BA43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC43" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="BD43" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.93</v>
+        <v>4.72</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="R44" t="n">
-        <v>2.24</v>
+        <v>1.63</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.99</v>
+        <v>1.79</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,133 +9272,133 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="R45" t="n">
-        <v>1.93</v>
+        <v>2.37</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.99</v>
+        <v>1.76</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.78</v>
+        <v>2.24</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR45" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AS45" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AU45" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AW45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AX45" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AY45" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BA45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF45" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,79 +9469,79 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.33</v>
+        <v>2.56</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.25</v>
+        <v>3.26</v>
       </c>
       <c r="R46" t="n">
-        <v>8</v>
+        <v>2.42</v>
       </c>
       <c r="S46" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>6.92</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.46</v>
+        <v>1.91</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.39</v>
+        <v>1.85</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9550,52 +9550,52 @@
         <v>0</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AT46" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AU46" t="n">
         <v>0</v>
       </c>
       <c r="AV46" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BA46" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD46" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BE46" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,133 +9666,133 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q47" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R47" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S47" t="n">
         <v>3.5</v>
       </c>
-      <c r="R47" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="S47" t="n">
+      <c r="T47" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W47" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X47" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU47" t="n">
         <v>3.25</v>
       </c>
-      <c r="T47" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U47" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V47" t="n">
+      <c r="AV47" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY47" t="n">
         <v>1.34</v>
       </c>
-      <c r="W47" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="X47" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN47" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AO47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW47" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AX47" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY47" t="n">
+      <c r="AZ47" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BB47" t="n">
         <v>1.27</v>
       </c>
-      <c r="AZ47" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BA47" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BB47" t="n">
-        <v>1.17</v>
-      </c>
       <c r="BC47" t="n">
-        <v>1.92</v>
+        <v>2.33</v>
       </c>
       <c r="BD47" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.52</v>
+        <v>3.34</v>
       </c>
       <c r="R48" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,79 +10060,79 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK49" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AL49" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AM49" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN49" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
@@ -10141,52 +10141,52 @@
         <v>0</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AT49" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AU49" t="n">
         <v>0</v>
       </c>
       <c r="AV49" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AW49" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AY49" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ49" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BA49" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC49" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD49" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,79 +10454,79 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL51" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AM51" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN51" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
@@ -10535,52 +10535,52 @@
         <v>0</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR51" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS51" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AU51" t="n">
         <v>0</v>
       </c>
       <c r="AV51" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AW51" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AX51" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AY51" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ51" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BA51" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="BB51" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC51" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD51" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE51" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BF51" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="Q52" t="n">
         <v>4</v>
       </c>
       <c r="R52" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10702,10 +10702,10 @@
         <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.23</v>
+        <v>2.63</v>
       </c>
       <c r="Q53" t="n">
-        <v>6.55</v>
+        <v>4</v>
       </c>
       <c r="R53" t="n">
-        <v>9.199999999999999</v>
+        <v>2.05</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.5</v>
+        <v>1.23</v>
       </c>
       <c r="Q54" t="n">
-        <v>4</v>
+        <v>6.55</v>
       </c>
       <c r="R54" t="n">
-        <v>2.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11096,10 +11096,10 @@
         <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -11251,124 +11251,124 @@
         <v>4.69</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>6.02</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AE55" t="n">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI55" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL55" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AM55" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN55" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO55" t="n">
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR55" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS55" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU55" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AV55" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW55" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AX55" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY55" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ55" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BA55" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BB55" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC55" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BD55" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE55" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF55" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14390,7 +14390,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16951,7 +16951,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G85" t="n">

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.8</v>
+        <v>1.87</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="R7" t="n">
-        <v>2.55</v>
+        <v>4.95</v>
       </c>
       <c r="S7" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="R8" t="n">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="S8" t="n">
-        <v>5.33</v>
+        <v>3.74</v>
       </c>
       <c r="T8" t="n">
-        <v>1.99</v>
+        <v>1.66</v>
       </c>
       <c r="U8" t="n">
-        <v>2.41</v>
+        <v>4.05</v>
       </c>
       <c r="V8" t="n">
-        <v>1.43</v>
+        <v>1.76</v>
       </c>
       <c r="W8" t="n">
-        <v>2.53</v>
+        <v>1.94</v>
       </c>
       <c r="X8" t="n">
-        <v>3.02</v>
+        <v>4.3</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.8</v>
+        <v>15</v>
       </c>
       <c r="AA8" t="n">
         <v>1.02</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.02</v>
       </c>
-      <c r="AC8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AK8" t="n">
-        <v>1.92</v>
+        <v>2.42</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.77</v>
+        <v>1.49</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.44</v>
+        <v>1.79</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.72</v>
+        <v>2.25</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.14</v>
+        <v>2.95</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.98</v>
+        <v>1.55</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.24</v>
+        <v>3.08</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.34</v>
+        <v>2.44</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="S9" t="n">
-        <v>3.38</v>
+        <v>3.78</v>
       </c>
       <c r="T9" t="n">
-        <v>2.03</v>
+        <v>1.78</v>
       </c>
       <c r="U9" t="n">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="V9" t="n">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="W9" t="n">
-        <v>2.66</v>
+        <v>2.24</v>
       </c>
       <c r="X9" t="n">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.01</v>
       </c>
-      <c r="AC9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD9" t="n">
+      <c r="AK9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BD9" t="n">
         <v>3.08</v>
       </c>
-      <c r="AE9" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BE9" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.7</v>
+        <v>3.29</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="S10" t="n">
-        <v>3.74</v>
+        <v>3.38</v>
       </c>
       <c r="T10" t="n">
-        <v>1.66</v>
+        <v>2.03</v>
       </c>
       <c r="U10" t="n">
-        <v>4.05</v>
+        <v>3.04</v>
       </c>
       <c r="V10" t="n">
-        <v>1.76</v>
+        <v>1.39</v>
       </c>
       <c r="W10" t="n">
-        <v>1.94</v>
+        <v>2.66</v>
       </c>
       <c r="X10" t="n">
-        <v>4.3</v>
+        <v>2.88</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="Z10" t="n">
-        <v>15</v>
+        <v>7.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.72</v>
+        <v>1.28</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>3.08</v>
       </c>
       <c r="AE10" t="n">
-        <v>3.46</v>
+        <v>1.99</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.29</v>
+        <v>1.78</v>
       </c>
       <c r="AG10" t="n">
-        <v>6</v>
+        <v>3.34</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="AI10" t="n">
-        <v>16</v>
+        <v>6.55</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.42</v>
+        <v>1.74</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.49</v>
+        <v>1.96</v>
       </c>
       <c r="AM10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN10" t="n">
         <v>1.41</v>
       </c>
-      <c r="AN10" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
         <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.08</v>
+        <v>2.17</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.44</v>
+        <v>3.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.87</v>
+        <v>4.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="R11" t="n">
-        <v>4.95</v>
+        <v>1.85</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2655,52 +2655,52 @@
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU11" t="n">
         <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R13" t="n">
         <v>3.8</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.1</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,22 +3362,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.93</v>
+        <v>3.64</v>
       </c>
       <c r="R15" t="n">
-        <v>4.47</v>
+        <v>3.74</v>
       </c>
       <c r="S15" t="n">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.27</v>
+        <v>2.36</v>
       </c>
       <c r="U15" t="n">
-        <v>4.81</v>
+        <v>4.34</v>
       </c>
       <c r="V15" t="n">
         <v>1.3</v>
@@ -3386,55 +3386,55 @@
         <v>3.16</v>
       </c>
       <c r="X15" t="n">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA15" t="n">
         <v>1.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.96</v>
+        <v>4.05</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AI15" t="n">
-        <v>4.45</v>
+        <v>4.9</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,16 +3476,16 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="BF15" t="n">
         <v>1.22</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,80 +3559,80 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.97</v>
+        <v>1.67</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.28</v>
+        <v>3.93</v>
       </c>
       <c r="R16" t="n">
-        <v>2.31</v>
+        <v>4.47</v>
       </c>
       <c r="S16" t="n">
-        <v>3.5</v>
+        <v>2.21</v>
       </c>
       <c r="T16" t="n">
-        <v>2.07</v>
+        <v>2.27</v>
       </c>
       <c r="U16" t="n">
-        <v>2.72</v>
+        <v>4.81</v>
       </c>
       <c r="V16" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>2.85</v>
+        <v>3.16</v>
       </c>
       <c r="X16" t="n">
-        <v>2.69</v>
+        <v>2.39</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AM16" t="n">
         <v>1.23</v>
       </c>
-      <c r="AD16" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AL16" t="n">
+      <c r="AN16" t="n">
         <v>2.1</v>
       </c>
-      <c r="AM16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BF16" t="n">
         <v>1.22</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1.88</v>
       </c>
-      <c r="Q17" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="R17" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U17" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W17" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.11</v>
-      </c>
       <c r="AG17" t="n">
-        <v>2.62</v>
+        <v>3.05</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.9</v>
+        <v>5.95</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="BD17" t="n">
         <v>4</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.91</v>
+        <v>3.13</v>
       </c>
       <c r="Q19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="S19" t="n">
         <v>3.25</v>
       </c>
-      <c r="R19" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.43</v>
-      </c>
       <c r="T19" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD19" t="n">
         <v>4.2</v>
       </c>
-      <c r="V19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BE19" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="R20" t="n">
-        <v>3.24</v>
+        <v>3.72</v>
       </c>
       <c r="S20" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="T20" t="n">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="U20" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X20" t="n">
-        <v>2.18</v>
+        <v>2.65</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AD20" t="n">
-        <v>4.25</v>
+        <v>3.35</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.38</v>
+        <v>3.15</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AI20" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.38</v>
+        <v>1.98</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="R23" t="n">
-        <v>3.72</v>
+        <v>3.24</v>
       </c>
       <c r="S23" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="T23" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="U23" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="V23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.65</v>
+        <v>2.18</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="Z23" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.35</v>
+        <v>4.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.15</v>
+        <v>2.38</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AI23" t="n">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.98</v>
+        <v>2.38</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,79 +5923,79 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6037,19 +6037,19 @@
         <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,79 +6120,79 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6234,19 +6234,19 @@
         <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6356,40 +6356,40 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>4.06</v>
+        <v>1.85</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="R31" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="S31" t="n">
-        <v>4.14</v>
+        <v>2.5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.29</v>
+        <v>2.06</v>
       </c>
       <c r="U31" t="n">
-        <v>2.36</v>
+        <v>4.4</v>
       </c>
       <c r="V31" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="W31" t="n">
-        <v>3.32</v>
+        <v>2.69</v>
       </c>
       <c r="X31" t="n">
-        <v>2.31</v>
+        <v>2.99</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AB31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>1.04</v>
       </c>
-      <c r="AC31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH31" t="n">
+      <c r="AK31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AX31" t="n">
         <v>1.5</v>
       </c>
-      <c r="AI31" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>0</v>
-      </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.82</v>
+        <v>2.27</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.88</v>
+        <v>1.59</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,79 +7499,79 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AD36" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AF36" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AI36" t="n">
-        <v>2.75</v>
+        <v>2.93</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.79</v>
+        <v>1.36</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.9</v>
+        <v>2.89</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="AN36" t="n">
-        <v>3.8</v>
+        <v>2.02</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
@@ -7613,19 +7613,19 @@
         <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,79 +7696,79 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
@@ -7810,19 +7810,19 @@
         <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BD37" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,79 +7893,79 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
@@ -8007,19 +8007,19 @@
         <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AS39" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AT39" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU39" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BA39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BD39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3.5</v>
+        <v>2.93</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="R40" t="n">
-        <v>1.98</v>
+        <v>2.24</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.16</v>
+        <v>3.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.24</v>
+        <v>3.52</v>
       </c>
       <c r="R41" t="n">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W42" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X42" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC42" t="n">
         <v>1.33</v>
       </c>
-      <c r="Q42" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="R42" t="n">
+      <c r="AD42" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI42" t="n">
         <v>8</v>
       </c>
-      <c r="S42" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U42" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W42" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="X42" t="n">
+      <c r="AJ42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS42" t="n">
         <v>2.25</v>
       </c>
-      <c r="Y42" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC42" t="n">
+      <c r="AT42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BF42" t="n">
         <v>1.1</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>1.28</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.93</v>
+        <v>2.56</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="R43" t="n">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>4.72</v>
+        <v>3.16</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.65</v>
+        <v>3.24</v>
       </c>
       <c r="R44" t="n">
-        <v>1.63</v>
+        <v>2.11</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,133 +9272,133 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="R45" t="n">
-        <v>2.37</v>
+        <v>1.93</v>
       </c>
       <c r="S45" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.76</v>
+        <v>1.99</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.24</v>
+        <v>1.78</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN45" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR45" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AS45" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AT45" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AU45" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AV45" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AW45" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AX45" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AY45" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ45" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BD45" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,133 +9469,133 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.56</v>
+        <v>1.33</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.26</v>
+        <v>5.25</v>
       </c>
       <c r="R46" t="n">
-        <v>2.42</v>
+        <v>8</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>6.92</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.91</v>
+        <v>1.46</v>
       </c>
       <c r="AF46" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AX46" t="n">
         <v>1.85</v>
       </c>
-      <c r="AG46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>0</v>
-      </c>
       <c r="AY46" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BA46" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BF46" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,133 +9666,133 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.78</v>
+        <v>4.72</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.24</v>
+        <v>3.65</v>
       </c>
       <c r="R47" t="n">
-        <v>2.48</v>
+        <v>1.63</v>
       </c>
       <c r="S47" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.19</v>
+        <v>1.79</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="AG47" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AS47" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AT47" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AU47" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV47" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AW47" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BA47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC47" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="BD47" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,133 +9863,133 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="R48" t="n">
-        <v>1.93</v>
+        <v>2.37</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.99</v>
+        <v>1.76</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.78</v>
+        <v>2.24</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR48" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AS48" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AU48" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AW48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AX48" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AY48" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BA48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BB48" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC48" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD48" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE48" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF48" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,79 +10060,79 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
@@ -10141,52 +10141,52 @@
         <v>0</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR49" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS49" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU49" t="n">
         <v>0</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY49" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BA49" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BB49" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC49" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BD49" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="BE49" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BF49" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,79 +10257,79 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI50" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AL50" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM50" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN50" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
@@ -10338,52 +10338,52 @@
         <v>0</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT50" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU50" t="n">
         <v>0</v>
       </c>
       <c r="AV50" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW50" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AY50" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ50" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BA50" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC50" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="BD50" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="Q52" t="n">
         <v>4</v>
       </c>
       <c r="R52" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10702,10 +10702,10 @@
         <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="Q53" t="n">
         <v>4</v>
       </c>
       <c r="R53" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16951,7 +16951,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G85" t="n">

--- a/jogos_2026-05-22.xlsx
+++ b/jogos_2026-05-22.xlsx
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.7</v>
+        <v>3.39</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.44</v>
+        <v>3.39</v>
       </c>
       <c r="R3" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1401,13 +1401,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U5" t="n">
-        <v>4.55</v>
+        <v>5.35</v>
       </c>
       <c r="V5" t="n">
         <v>1.35</v>
@@ -1428,7 +1428,7 @@
         <v>1.04</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC5" t="n">
         <v>1.22</v>
@@ -1437,10 +1437,10 @@
         <v>3.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AG5" t="n">
         <v>3.04</v>
@@ -1449,22 +1449,22 @@
         <v>1.29</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.9</v>
+        <v>5.85</v>
       </c>
       <c r="AJ5" t="n">
         <v>1.07</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.89</v>
+        <v>2.12</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1509,13 +1509,13 @@
         <v>1.17</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="BF5" t="n">
         <v>1.15</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="R7" t="n">
-        <v>4.95</v>
+        <v>3.3</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1983,28 +1983,28 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.7</v>
+        <v>2.51</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="S8" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="T8" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U8" t="n">
         <v>4.05</v>
       </c>
       <c r="V8" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="W8" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="X8" t="n">
         <v>4.3</v>
@@ -2013,31 +2013,31 @@
         <v>1.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AE8" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AG8" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AI8" t="n">
         <v>16</v>
@@ -2049,7 +2049,7 @@
         <v>2.42</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AM8" t="n">
         <v>1.41</v>
@@ -2100,16 +2100,16 @@
         <v>1.46</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="BD8" t="n">
         <v>2.44</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="R9" t="n">
-        <v>2.55</v>
+        <v>1.94</v>
       </c>
       <c r="S9" t="n">
-        <v>3.78</v>
+        <v>5.08</v>
       </c>
       <c r="T9" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="U9" t="n">
-        <v>3.44</v>
+        <v>2.7</v>
       </c>
       <c r="V9" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W9" t="n">
-        <v>2.24</v>
+        <v>2.33</v>
       </c>
       <c r="X9" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z9" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG9" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AH9" t="n">
         <v>1.15</v>
       </c>
       <c r="AI9" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AJ9" t="n">
         <v>1.01</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="BC9" t="n">
         <v>2.41</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="BE9" t="n">
         <v>1.47</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,130 +2377,130 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.76</v>
+        <v>4.41</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5</v>
+        <v>1.76</v>
       </c>
       <c r="S10" t="n">
-        <v>3.38</v>
+        <v>5.33</v>
       </c>
       <c r="T10" t="n">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="U10" t="n">
-        <v>3.04</v>
+        <v>2.41</v>
       </c>
       <c r="V10" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W10" t="n">
-        <v>2.66</v>
+        <v>2.53</v>
       </c>
       <c r="X10" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD10" t="n">
         <v>2.88</v>
       </c>
-      <c r="Y10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>3.08</v>
-      </c>
       <c r="AE10" t="n">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AG10" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BD10" t="n">
         <v>3.34</v>
       </c>
-      <c r="AH10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BE10" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="BF10" t="n">
         <v>1.12</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>4.33</v>
+        <v>2.81</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.4</v>
+        <v>3.29</v>
       </c>
       <c r="R11" t="n">
-        <v>1.85</v>
+        <v>2.46</v>
       </c>
       <c r="S11" t="n">
-        <v>5.33</v>
+        <v>3.42</v>
       </c>
       <c r="T11" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="U11" t="n">
-        <v>2.41</v>
+        <v>3.02</v>
       </c>
       <c r="V11" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W11" t="n">
-        <v>2.53</v>
+        <v>2.66</v>
       </c>
       <c r="X11" t="n">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Z11" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AI11" t="n">
-        <v>7.1</v>
+        <v>6.55</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.77</v>
+        <v>1.96</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2655,52 +2655,52 @@
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
         <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE11" t="n">
         <v>1.61</v>
       </c>
-      <c r="AY11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.57</v>
-      </c>
       <c r="BF11" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AY12" t="n">
         <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.93</v>
+        <v>2.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="R13" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>6.64</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.88</v>
       </c>
-      <c r="Q15" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="R15" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U15" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W15" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.11</v>
-      </c>
       <c r="AG15" t="n">
-        <v>2.62</v>
+        <v>3.05</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AI15" t="n">
-        <v>4.9</v>
+        <v>5.95</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="BD15" t="n">
         <v>4</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.97</v>
+        <v>1.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.28</v>
+        <v>3.64</v>
       </c>
       <c r="R17" t="n">
-        <v>2.31</v>
+        <v>3.74</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.07</v>
+        <v>2.36</v>
       </c>
       <c r="U17" t="n">
-        <v>2.72</v>
+        <v>4.34</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W17" t="n">
-        <v>2.85</v>
+        <v>3.16</v>
       </c>
       <c r="X17" t="n">
-        <v>2.69</v>
+        <v>2.44</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.42</v>
+        <v>4.05</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AI17" t="n">
-        <v>5.95</v>
+        <v>4.9</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="BD17" t="n">
         <v>4</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.13</v>
+        <v>2.39</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>2.16</v>
+        <v>2.93</v>
       </c>
       <c r="S19" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="T19" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="V19" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="W19" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="X19" t="n">
-        <v>2.63</v>
+        <v>3.05</v>
       </c>
       <c r="Y19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC19" t="n">
         <v>1.38</v>
       </c>
-      <c r="Z19" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AD19" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.84</v>
+        <v>2.17</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="AH19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM19" t="n">
         <v>1.3</v>
       </c>
-      <c r="AI19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK19" t="n">
+      <c r="AN19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AW19" t="n">
         <v>1.64</v>
       </c>
-      <c r="AL19" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW19" t="n">
+      <c r="AX19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ19" t="n">
         <v>2</v>
       </c>
-      <c r="AX19" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ19" t="n">
+      <c r="BA19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BC19" t="n">
         <v>2.38</v>
       </c>
-      <c r="BA19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>2.05</v>
-      </c>
       <c r="BD19" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.98</v>